--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_262_R27.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_262_R27.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5487</v>
+        <v>4.7819</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4823</v>
+        <v>4.0852</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0665</v>
+        <v>0.6968</v>
       </c>
       <c r="G2" t="n">
         <v>3.1051</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6576</v>
+        <v>-0.1092</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6765</v>
+        <v>0.2794</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0189</v>
+        <v>-0.3886</v>
       </c>
       <c r="V2" t="n">
         <v>0.3943</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1668</v>
+        <v>3.2916</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8187</v>
+        <v>1.7754</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3482</v>
+        <v>1.5162</v>
       </c>
       <c r="G3" t="n">
         <v>3.4254</v>
@@ -688,13 +688,13 @@
         <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1357</v>
+        <v>0.2605</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0351</v>
+        <v>-0.0784</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1709</v>
+        <v>0.3389</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3943</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W. GABRIEL</t>
+          <t>A. OBST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9507</v>
+        <v>2.6737</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2407</v>
+        <v>0.8924</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2901</v>
+        <v>1.7813</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.608</v>
+        <v>0.4398</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8285</v>
+        <v>-3.4514</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7794</v>
+        <v>3.8912</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4292</v>
+        <v>1.3334</v>
       </c>
       <c r="K4" t="n">
-        <v>0.098</v>
+        <v>-2.6714</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3312</v>
+        <v>4.0047</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0372</v>
+        <v>-0.8935999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9265</v>
+        <v>-0.78</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1107</v>
+        <v>-0.1136</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3195</v>
+        <v>1.6237</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3195</v>
+        <v>3.0154</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2391</v>
+        <v>-0.4619</v>
       </c>
       <c r="T4" t="n">
-        <v>2.8115</v>
+        <v>-0.1215</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5724</v>
+        <v>-0.3404</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. OBST</t>
+          <t>N. GIFFEY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9689</v>
+        <v>1.5904</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3892</v>
+        <v>2.3999</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5797</v>
+        <v>-0.8095</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4398</v>
+        <v>0.2456</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.4514</v>
+        <v>0.9449</v>
       </c>
       <c r="I5" t="n">
-        <v>3.8912</v>
+        <v>-0.6993</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3334</v>
+        <v>2.1007</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.6714</v>
+        <v>1.378</v>
       </c>
       <c r="L5" t="n">
-        <v>4.0047</v>
+        <v>0.7227</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8935999999999999</v>
+        <v>-1.8551</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.78</v>
+        <v>-0.4331</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1136</v>
+        <v>-1.422</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R5" t="n">
-        <v>3.0154</v>
+        <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1668</v>
+        <v>0.0433</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6247</v>
+        <v>0.3894</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5421</v>
+        <v>-0.3462</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. GIFFEY</t>
+          <t>J. VOIGTMANN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.338</v>
+        <v>1.4666</v>
       </c>
       <c r="E6" t="n">
-        <v>2.282</v>
+        <v>0.2243</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.944</v>
+        <v>1.2423</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2456</v>
+        <v>0.8661</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9449</v>
+        <v>0.0396</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6993</v>
+        <v>0.8264</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1007</v>
+        <v>0.405</v>
       </c>
       <c r="K6" t="n">
-        <v>1.378</v>
+        <v>0.0504</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7227</v>
+        <v>0.3546</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8551</v>
+        <v>0.461</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4331</v>
+        <v>-0.0108</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.422</v>
+        <v>0.4718</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2091</v>
+        <v>0.1366</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2715</v>
+        <v>-0.1808</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4806</v>
+        <v>0.3174</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. VOIGTMANN</t>
+          <t>J. HOLLATZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3075</v>
+        <v>1.1269</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0316</v>
+        <v>3.4028</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2759</v>
+        <v>-2.2759</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8661</v>
+        <v>2.257</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0396</v>
+        <v>0.2762</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8264</v>
+        <v>1.9808</v>
       </c>
       <c r="J7" t="n">
-        <v>0.405</v>
+        <v>3.3005</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0504</v>
+        <v>0.3193</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3546</v>
+        <v>2.9812</v>
       </c>
       <c r="M7" t="n">
-        <v>0.461</v>
+        <v>-1.0435</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0108</v>
+        <v>-0.0431</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4718</v>
+        <v>-1.0004</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0224</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3734</v>
+        <v>0.3343</v>
       </c>
       <c r="U7" t="n">
-        <v>0.351</v>
+        <v>-0.2478</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. HOLLATZ</t>
+          <t>W. GABRIEL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2284</v>
+        <v>0.9701</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6388</v>
+        <v>1.4282</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4103</v>
+        <v>-0.4581</v>
       </c>
       <c r="G8" t="n">
-        <v>2.257</v>
+        <v>-1.608</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2762</v>
+        <v>-0.8285</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9808</v>
+        <v>-0.7794</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3005</v>
+        <v>0.4292</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3193</v>
+        <v>0.098</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9812</v>
+        <v>0.3312</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0435</v>
+        <v>-2.0372</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0431</v>
+        <v>-0.9265</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0004</v>
+        <v>-1.1107</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9278</v>
+        <v>2.3195</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1598</v>
+        <v>2.3195</v>
       </c>
       <c r="S8" t="n">
-        <v>0.188</v>
+        <v>0.2585</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5702</v>
+        <v>0.999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3822</v>
+        <v>-0.7403999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8746</v>
+        <v>-0.1601</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4602</v>
+        <v>2.0067</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3348</v>
+        <v>-2.1668</v>
       </c>
       <c r="G9" t="n">
         <v>1.4877</v>
@@ -1156,13 +1156,13 @@
         <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5942</v>
+        <v>-0.8797</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5975</v>
+        <v>-0.051</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9968</v>
+        <v>-0.8287</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5361</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. MCCORMACK</t>
+          <t>I. MIKE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5766</v>
+        <v>-1.2935</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2533</v>
+        <v>-1.2511</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6767</v>
+        <v>-0.0423</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3322</v>
+        <v>-3.1765</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0444</v>
+        <v>-0.3925</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2878</v>
+        <v>-2.784</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4396</v>
+        <v>-1.6435</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2556</v>
+        <v>-0.1275</v>
       </c>
       <c r="L10" t="n">
-        <v>0.184</v>
+        <v>-1.516</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1074</v>
+        <v>-1.533</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2112</v>
+        <v>-0.2651</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1038</v>
+        <v>-1.2679</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0876</v>
+        <v>2.3195</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.5515</v>
+        <v>-0.232</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4639</v>
+        <v>2.5515</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1788</v>
+        <v>-0.4364</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1415</v>
+        <v>-0.4479</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3203</v>
+        <v>0.0114</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. MIKE</t>
+          <t>J. JESSUP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6293</v>
+        <v>-1.5897</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9902</v>
+        <v>-1.1067</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3609</v>
+        <v>-0.483</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.1765</v>
+        <v>-0.586</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3925</v>
+        <v>-1.5629</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.784</v>
+        <v>0.9769</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.6435</v>
+        <v>0.0185</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1275</v>
+        <v>-0.3326</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.516</v>
+        <v>0.3511</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.533</v>
+        <v>-0.6044</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2651</v>
+        <v>-1.2303</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.2679</v>
+        <v>0.6258</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3195</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.232</v>
+        <v>-2.3195</v>
       </c>
       <c r="R11" t="n">
-        <v>2.5515</v>
+        <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7723</v>
+        <v>-0.1867</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.187</v>
+        <v>0.1221</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4147</v>
+        <v>-0.3088</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1107</v>
       </c>
       <c r="W11" t="n">
         <v>1.0722</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0722</v>
+        <v>-0.9615</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. JESSUP</t>
+          <t>D. MCCORMACK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9441</v>
+        <v>-1.6267</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.125</v>
+        <v>-2.1354</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8191000000000001</v>
+        <v>0.5087</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.586</v>
+        <v>0.3322</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.5629</v>
+        <v>0.0444</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9769</v>
+        <v>0.2878</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0185</v>
+        <v>0.4396</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3326</v>
+        <v>0.2556</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3511</v>
+        <v>0.184</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6044</v>
+        <v>-0.1074</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.2303</v>
+        <v>-0.2112</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6258</v>
+        <v>0.1038</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9278</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.3195</v>
+        <v>-2.5515</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5411</v>
+        <v>0.1287</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8962</v>
+        <v>-0.0235</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6449</v>
+        <v>0.1522</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1107</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.9615</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.4844</v>
+        <v>11.2312</v>
       </c>
       <c r="E13" t="n">
-        <v>10.975</v>
+        <v>11.7217</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4903999999999999</v>
+        <v>-0.4903</v>
       </c>
       <c r="G13" t="n">
         <v>6.788399999999998</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.9856</v>
+        <v>-3.985599999999999</v>
       </c>
       <c r="I13" t="n">
         <v>10.774</v>
@@ -1444,7 +1444,7 @@
         <v>15.2062</v>
       </c>
       <c r="K13" t="n">
-        <v>1.756599999999999</v>
+        <v>1.7566</v>
       </c>
       <c r="L13" t="n">
         <v>13.4495</v>
@@ -1462,16 +1462,16 @@
         <v>6.958500000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-9.2783</v>
+        <v>-9.278300000000002</v>
       </c>
       <c r="R13" t="n">
         <v>16.2367</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.9067</v>
+        <v>-1.1598</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4742999999999996</v>
+        <v>1.2211</v>
       </c>
       <c r="U13" t="n">
         <v>-2.381</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.0868</v>
+        <v>5.6587</v>
       </c>
       <c r="E14" t="n">
-        <v>5.1149</v>
+        <v>5.3508</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0282</v>
+        <v>0.3079</v>
       </c>
       <c r="G14" t="n">
         <v>2.9884</v>
@@ -1546,13 +1546,13 @@
         <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1336</v>
+        <v>0.4384</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1968</v>
+        <v>0.4327</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3304</v>
+        <v>0.0057</v>
       </c>
       <c r="V14" t="n">
         <v>1.0722</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. BEGARIN</t>
+          <t>M. JAMES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4077</v>
+        <v>1.3136</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0501</v>
+        <v>3.4873</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3576</v>
+        <v>-2.1737</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.4642</v>
+        <v>1.8844</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.1056</v>
+        <v>1.6034</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.3585</v>
+        <v>0.281</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.2318</v>
+        <v>5.0901</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.7695</v>
+        <v>2.3835</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.4623</v>
+        <v>2.7066</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2323</v>
+        <v>-3.2056</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3361</v>
+        <v>-0.78</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1038</v>
+        <v>-2.4256</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7997</v>
+        <v>0.3027</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2097</v>
+        <v>-0.0154</v>
       </c>
       <c r="U15" t="n">
-        <v>0.59</v>
+        <v>0.3181</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0722</v>
+        <v>1.214</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0722</v>
+        <v>1.8919</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. JAMES</t>
+          <t>T. TARPEY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.583</v>
+        <v>0.2273</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7796</v>
+        <v>-0.1536</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.1966</v>
+        <v>0.3809</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8844</v>
+        <v>0.6244</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6034</v>
+        <v>0.4839</v>
       </c>
       <c r="I16" t="n">
-        <v>0.281</v>
+        <v>0.1406</v>
       </c>
       <c r="J16" t="n">
-        <v>5.0901</v>
+        <v>0.0704</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3835</v>
+        <v>0.0336</v>
       </c>
       <c r="L16" t="n">
-        <v>2.7066</v>
+        <v>0.0368</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.2056</v>
+        <v>0.554</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.78</v>
+        <v>0.4502</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.4256</v>
+        <v>0.1038</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.0876</v>
+        <v>0.232</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4279</v>
+        <v>-0.6291</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7231</v>
+        <v>-0.224</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2952</v>
+        <v>-0.405</v>
       </c>
       <c r="V16" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8919</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. TARPEY</t>
+          <t>J. BEGARIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0929</v>
+        <v>-0.243</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1536</v>
+        <v>-0.3654</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2465</v>
+        <v>0.1224</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6244</v>
+        <v>-2.4642</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4839</v>
+        <v>-1.1056</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1406</v>
+        <v>-1.3585</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0704</v>
+        <v>-2.2318</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0336</v>
+        <v>-0.7695</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0368</v>
+        <v>-1.4623</v>
       </c>
       <c r="M17" t="n">
-        <v>0.554</v>
+        <v>-0.2323</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4502</v>
+        <v>-0.3361</v>
       </c>
       <c r="O17" t="n">
         <v>0.1038</v>
       </c>
       <c r="P17" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7635</v>
+        <v>1.149</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.224</v>
+        <v>0.7943</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5395</v>
+        <v>0.3547</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0596</v>
+        <v>-0.3792</v>
       </c>
       <c r="E18" t="n">
-        <v>0.028</v>
+        <v>-0.09</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0876</v>
+        <v>-0.2892</v>
       </c>
       <c r="G18" t="n">
         <v>-1.1362</v>
@@ -1858,13 +1858,13 @@
         <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4709</v>
+        <v>0.1513</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4288</v>
+        <v>0.3108</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0422</v>
+        <v>-0.1595</v>
       </c>
       <c r="V18" t="n">
         <v>0.1418</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5887</v>
+        <v>-1.3916</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1407</v>
+        <v>0.3151</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7295</v>
+        <v>-1.7066</v>
       </c>
       <c r="G19" t="n">
         <v>-1.1332</v>
@@ -1936,13 +1936,13 @@
         <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1527</v>
+        <v>0.3499</v>
       </c>
       <c r="T19" t="n">
-        <v>1.404</v>
+        <v>0.5783</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2513</v>
+        <v>-0.2284</v>
       </c>
       <c r="V19" t="n">
         <v>-1.0722</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4392</v>
+        <v>-1.5977</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8250999999999999</v>
+        <v>-0.3533</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6141</v>
+        <v>-1.2444</v>
       </c>
       <c r="G20" t="n">
         <v>1.3218</v>
@@ -2014,13 +2014,13 @@
         <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6012</v>
+        <v>-0.7598</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6642</v>
+        <v>-0.1924</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-0.5673</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5361</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.9784</v>
+        <v>-2.5579</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.873</v>
+        <v>-1.8115</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1054</v>
+        <v>-0.7465000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>-2.399</v>
@@ -2092,13 +2092,13 @@
         <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7934</v>
+        <v>0.6271</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5658</v>
+        <v>0.4957</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2275</v>
+        <v>0.1314</v>
       </c>
       <c r="V21" t="n">
         <v>0.1418</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1737</v>
+        <v>-4.622</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4874</v>
+        <v>-3.7233</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6862</v>
+        <v>-0.8986</v>
       </c>
       <c r="G22" t="n">
         <v>-4.6663</v>
@@ -2170,13 +2170,13 @@
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>1.3456</v>
+        <v>0.8973</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5192</v>
+        <v>0.2833</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8263</v>
+        <v>0.6139</v>
       </c>
       <c r="V22" t="n">
         <v>1.4665</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.4152</v>
+        <v>-6.1064</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2837</v>
+        <v>-2.1657</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.1315</v>
+        <v>-3.9407</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8085</v>
@@ -2248,13 +2248,13 @@
         <v>0.232</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1428</v>
+        <v>0.1661</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2003</v>
+        <v>-0.0824</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0576</v>
+        <v>0.2484</v>
       </c>
       <c r="V23" t="n">
         <v>-2.1444</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.4844</v>
+        <v>-9.6982</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4904999999999986</v>
+        <v>0.4903999999999984</v>
       </c>
       <c r="F24" t="n">
-        <v>-10.975</v>
+        <v>-10.1885</v>
       </c>
       <c r="G24" t="n">
         <v>-6.788399999999999</v>
@@ -2302,7 +2302,7 @@
         <v>8.4178</v>
       </c>
       <c r="K24" t="n">
-        <v>5.7425</v>
+        <v>5.742500000000001</v>
       </c>
       <c r="L24" t="n">
         <v>2.6755</v>
@@ -2326,13 +2326,13 @@
         <v>9.2783</v>
       </c>
       <c r="S24" t="n">
-        <v>1.9065</v>
+        <v>2.6929</v>
       </c>
       <c r="T24" t="n">
-        <v>2.381100000000001</v>
+        <v>2.3809</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4744000000000003</v>
+        <v>0.3119999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>1.3558</v>
